--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08442D99-97B1-43BB-8DD2-2E411E04AF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF005D91-77FF-4FC6-955C-3E3BF948F394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF005D91-77FF-4FC6-955C-3E3BF948F394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0869A018-91A1-4626-A86A-7F79F3830F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0869A018-91A1-4626-A86A-7F79F3830F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542FB07C-D6FB-4820-AFAD-1B0A4519D940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542FB07C-D6FB-4820-AFAD-1B0A4519D940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AFD542-3776-4DCB-89D2-B030A9C62750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AFD542-3776-4DCB-89D2-B030A9C62750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB8ABA9-F2C3-476B-9718-2F616761EE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB8ABA9-F2C3-476B-9718-2F616761EE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262C4F14-1639-49ED-999E-7308B3BDF902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262C4F14-1639-49ED-999E-7308B3BDF902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EADA1D5-7922-4E93-BE16-D27891DFBC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EADA1D5-7922-4E93-BE16-D27891DFBC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05775309-47B3-4D5F-9DC6-4D975EC2B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05775309-47B3-4D5F-9DC6-4D975EC2B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B094B02C-1F59-41C2-86C6-DA1B4C9005D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B094B02C-1F59-41C2-86C6-DA1B4C9005D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FB3CE7-EA97-4274-A07E-C2C09F2099A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FB3CE7-EA97-4274-A07E-C2C09F2099A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3108AFD7-D8DF-4AE2-84A4-32993FEC9328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3108AFD7-D8DF-4AE2-84A4-32993FEC9328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C694C5-C437-49D8-A14A-F92577C31E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C694C5-C437-49D8-A14A-F92577C31E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045CCBED-A9F9-4B22-8A3D-CACD334388D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045CCBED-A9F9-4B22-8A3D-CACD334388D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC52F818-9037-4C3B-B475-79B4C69D4A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC52F818-9037-4C3B-B475-79B4C69D4A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4563BE1-E636-419B-99AE-C8D4A2F82979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="255">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -682,19 +682,127 @@
     <t>set</t>
   </si>
   <si>
-    <t>elc_spv-CHE</t>
-  </si>
-  <si>
-    <t>solar electricity generation</t>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_won-CHE</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation</t>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 10</t>
   </si>
 </sst>
 </file>
@@ -3254,6 +3362,24 @@
       <c r="E7" t="s">
         <v>18</v>
       </c>
+      <c r="M7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O7" t="s">
+        <v>220</v>
+      </c>
+      <c r="P7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="8" spans="2:18">
       <c r="B8" t="s">
@@ -3265,6 +3391,24 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O8" t="s">
+        <v>222</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="9" spans="2:18">
       <c r="B9" t="s">
@@ -3276,6 +3420,24 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O9" t="s">
+        <v>224</v>
+      </c>
+      <c r="P9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="10" spans="2:18">
       <c r="B10" t="s">
@@ -3287,6 +3449,24 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" t="s">
@@ -3298,6 +3478,24 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>227</v>
+      </c>
+      <c r="O11" t="s">
+        <v>228</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" t="s">
@@ -3309,6 +3507,24 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>229</v>
+      </c>
+      <c r="O12" t="s">
+        <v>230</v>
+      </c>
+      <c r="P12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" t="s">
@@ -3320,6 +3536,24 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" t="s">
+        <v>232</v>
+      </c>
+      <c r="P13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
@@ -3334,6 +3568,24 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" t="s">
+        <v>234</v>
+      </c>
+      <c r="P14" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="15" spans="2:18">
       <c r="B15" t="s">
@@ -3348,6 +3600,24 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" t="s">
+        <v>236</v>
+      </c>
+      <c r="P15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="16" spans="2:18">
       <c r="B16" t="s">
@@ -3371,8 +3641,26 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>237</v>
+      </c>
+      <c r="O16" t="s">
+        <v>238</v>
+      </c>
+      <c r="P16" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -3385,8 +3673,26 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17" t="s">
+        <v>240</v>
+      </c>
+      <c r="P17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3399,8 +3705,26 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>241</v>
+      </c>
+      <c r="O18" t="s">
+        <v>242</v>
+      </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3413,8 +3737,26 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>243</v>
+      </c>
+      <c r="O19" t="s">
+        <v>244</v>
+      </c>
+      <c r="P19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3427,8 +3769,26 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P20" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -3447,8 +3807,26 @@
       <c r="G21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="M21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>247</v>
+      </c>
+      <c r="O21" t="s">
+        <v>248</v>
+      </c>
+      <c r="P21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>193</v>
       </c>
@@ -3461,8 +3839,26 @@
       <c r="E22" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s">
+        <v>250</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>193</v>
       </c>
@@ -3472,8 +3868,26 @@
       <c r="E23" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>251</v>
+      </c>
+      <c r="O23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>193</v>
       </c>
@@ -3482,6 +3896,24 @@
       </c>
       <c r="E24" t="s">
         <v>196</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" t="s">
+        <v>254</v>
+      </c>
+      <c r="P24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4563BE1-E636-419B-99AE-C8D4A2F82979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF745E85-6FC6-4EA4-93FD-45A8FFF3BB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF745E85-6FC6-4EA4-93FD-45A8FFF3BB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA04ECD-8462-4BDC-8C05-F63047F43A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA04ECD-8462-4BDC-8C05-F63047F43A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB0A500-9CC6-44CF-B407-8E1E17CA2388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB0A500-9CC6-44CF-B407-8E1E17CA2388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A6F08C-D34D-4AB2-8403-E6ABE02DFC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A6F08C-D34D-4AB2-8403-E6ABE02DFC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B694F6A2-7240-477C-AF5E-F7816D54E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B694F6A2-7240-477C-AF5E-F7816D54E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F5DA93-3CB4-412B-A6EE-A2C2C48C887C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SysSettings.xlsx
+++ b/VerveStacks_CHE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F5DA93-3CB4-412B-A6EE-A2C2C48C887C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A502576-AAEE-4EA7-8559-E841FDC5DA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
